--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{0B714118-85B2-4EBF-AAE3-8776E3C3B256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEB900EE-22C2-462C-B87B-62F923642E3C}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB1AA658-C141-4B36-859C-D1C0A4DE24AE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1978,11 +1978,11 @@
         <v>28</v>
       </c>
       <c r="C30" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="9">
         <f>C30-B30</f>
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="E30">
         <v>41</v>
@@ -2033,11 +2033,11 @@
         <v>21</v>
       </c>
       <c r="C31" s="1">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D31" s="9">
         <f t="shared" ref="D31:D40" si="8">C31-B31</f>
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="E31">
         <v>29</v>
@@ -2088,11 +2088,11 @@
         <v>22</v>
       </c>
       <c r="C32" s="1">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D32" s="9">
         <f t="shared" si="8"/>
-        <v>-17</v>
+        <v>-8</v>
       </c>
       <c r="E32">
         <v>33</v>
@@ -2143,11 +2143,11 @@
         <v>37</v>
       </c>
       <c r="C33" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D33" s="9">
         <f t="shared" si="8"/>
-        <v>-31</v>
+        <v>-24</v>
       </c>
       <c r="E33">
         <v>55</v>
@@ -2198,11 +2198,11 @@
         <v>23</v>
       </c>
       <c r="C34" s="1">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D34" s="9">
         <f t="shared" si="8"/>
-        <v>-22</v>
+        <v>-10</v>
       </c>
       <c r="E34">
         <v>34</v>
@@ -2253,11 +2253,11 @@
         <v>24</v>
       </c>
       <c r="C35" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D35" s="9">
         <f t="shared" si="8"/>
-        <v>-18</v>
+        <v>-13</v>
       </c>
       <c r="E35">
         <v>37</v>
@@ -2308,11 +2308,11 @@
         <v>25</v>
       </c>
       <c r="C36" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D36" s="9">
         <f t="shared" si="8"/>
-        <v>-22</v>
+        <v>-18</v>
       </c>
       <c r="E36">
         <v>37</v>
@@ -2363,11 +2363,11 @@
         <v>39</v>
       </c>
       <c r="C37" s="1">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D37" s="9">
         <f t="shared" si="8"/>
-        <v>-35</v>
+        <v>-27</v>
       </c>
       <c r="E37">
         <v>59</v>
@@ -2418,11 +2418,11 @@
         <v>27</v>
       </c>
       <c r="C38" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D38" s="9">
         <f t="shared" si="8"/>
-        <v>-27</v>
+        <v>-21</v>
       </c>
       <c r="E38">
         <v>41</v>
@@ -2473,11 +2473,11 @@
         <v>27</v>
       </c>
       <c r="C39" s="1">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D39" s="9">
         <f t="shared" si="8"/>
-        <v>-21</v>
+        <v>-10</v>
       </c>
       <c r="E39">
         <v>41</v>
@@ -2528,11 +2528,11 @@
         <v>9</v>
       </c>
       <c r="C40" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="8"/>
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="E40">
         <v>13</v>
@@ -2578,11 +2578,11 @@
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C42">
         <f>SUM(C30:C41)</f>
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="D42">
         <f>SUM(D30:D41)</f>
-        <v>-248</v>
+        <v>-169</v>
       </c>
       <c r="G42">
         <f>SUM(G30:G41)</f>

--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB1AA658-C141-4B36-859C-D1C0A4DE24AE}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FC06B06-DB1A-475D-A6CF-AE19060EDBB3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FC06B06-DB1A-475D-A6CF-AE19060EDBB3}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1A7CCB4-496C-4428-A999-D91DBB8D618B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1978,11 +1978,11 @@
         <v>28</v>
       </c>
       <c r="C30" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D30" s="9">
         <f>C30-B30</f>
-        <v>-27</v>
+        <v>-16</v>
       </c>
       <c r="E30">
         <v>41</v>
@@ -2033,11 +2033,11 @@
         <v>21</v>
       </c>
       <c r="C31" s="1">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D31" s="9">
         <f t="shared" ref="D31:D40" si="8">C31-B31</f>
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="E31">
         <v>29</v>
@@ -2088,11 +2088,11 @@
         <v>22</v>
       </c>
       <c r="C32" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D32" s="9">
         <f t="shared" si="8"/>
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="E32">
         <v>33</v>
@@ -2143,11 +2143,11 @@
         <v>37</v>
       </c>
       <c r="C33" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D33" s="9">
         <f t="shared" si="8"/>
-        <v>-24</v>
+        <v>-21</v>
       </c>
       <c r="E33">
         <v>55</v>
@@ -2198,11 +2198,11 @@
         <v>23</v>
       </c>
       <c r="C34" s="1">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D34" s="9">
         <f t="shared" si="8"/>
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="E34">
         <v>34</v>
@@ -2253,11 +2253,11 @@
         <v>24</v>
       </c>
       <c r="C35" s="1">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D35" s="9">
         <f t="shared" si="8"/>
-        <v>-13</v>
+        <v>-6</v>
       </c>
       <c r="E35">
         <v>37</v>
@@ -2308,11 +2308,11 @@
         <v>25</v>
       </c>
       <c r="C36" s="1">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D36" s="9">
         <f t="shared" si="8"/>
-        <v>-18</v>
+        <v>-9</v>
       </c>
       <c r="E36">
         <v>37</v>
@@ -2363,11 +2363,11 @@
         <v>39</v>
       </c>
       <c r="C37" s="1">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D37" s="9">
         <f t="shared" si="8"/>
-        <v>-27</v>
+        <v>-21</v>
       </c>
       <c r="E37">
         <v>59</v>
@@ -2418,11 +2418,11 @@
         <v>27</v>
       </c>
       <c r="C38" s="1">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D38" s="9">
         <f t="shared" si="8"/>
-        <v>-21</v>
+        <v>-13</v>
       </c>
       <c r="E38">
         <v>41</v>
@@ -2473,11 +2473,11 @@
         <v>27</v>
       </c>
       <c r="C39" s="1">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D39" s="9">
         <f t="shared" si="8"/>
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="E39">
         <v>41</v>
@@ -2528,11 +2528,11 @@
         <v>9</v>
       </c>
       <c r="C40" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="8"/>
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="E40">
         <v>13</v>
@@ -2578,11 +2578,11 @@
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C42">
         <f>SUM(C30:C41)</f>
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="D42">
         <f>SUM(D30:D41)</f>
-        <v>-169</v>
+        <v>-103</v>
       </c>
       <c r="G42">
         <f>SUM(G30:G41)</f>

--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1A7CCB4-496C-4428-A999-D91DBB8D618B}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16BD902C-A54B-4E15-8DBE-20F8F347314B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="13416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Order Bank Targets" sheetId="1" r:id="rId1"/>
@@ -1978,11 +1978,11 @@
         <v>28</v>
       </c>
       <c r="C30" s="1">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D30" s="9">
         <f>C30-B30</f>
-        <v>-16</v>
+        <v>-5</v>
       </c>
       <c r="E30">
         <v>41</v>
@@ -2033,11 +2033,11 @@
         <v>21</v>
       </c>
       <c r="C31" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D31" s="9">
         <f t="shared" ref="D31:D40" si="8">C31-B31</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>29</v>
@@ -2088,11 +2088,11 @@
         <v>22</v>
       </c>
       <c r="C32" s="1">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D32" s="9">
         <f t="shared" si="8"/>
-        <v>-4</v>
+        <v>10</v>
       </c>
       <c r="E32">
         <v>33</v>
@@ -2143,11 +2143,11 @@
         <v>37</v>
       </c>
       <c r="C33" s="1">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D33" s="9">
         <f t="shared" si="8"/>
-        <v>-21</v>
+        <v>-14</v>
       </c>
       <c r="E33">
         <v>55</v>
@@ -2198,11 +2198,11 @@
         <v>23</v>
       </c>
       <c r="C34" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D34" s="9">
         <f t="shared" si="8"/>
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="E34">
         <v>34</v>
@@ -2253,11 +2253,11 @@
         <v>24</v>
       </c>
       <c r="C35" s="1">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D35" s="9">
         <f t="shared" si="8"/>
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="E35">
         <v>37</v>
@@ -2308,11 +2308,11 @@
         <v>25</v>
       </c>
       <c r="C36" s="1">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D36" s="9">
         <f t="shared" si="8"/>
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>37</v>
@@ -2363,11 +2363,11 @@
         <v>39</v>
       </c>
       <c r="C37" s="1">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D37" s="9">
         <f t="shared" si="8"/>
-        <v>-21</v>
+        <v>-4</v>
       </c>
       <c r="E37">
         <v>59</v>
@@ -2418,11 +2418,11 @@
         <v>27</v>
       </c>
       <c r="C38" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D38" s="9">
         <f t="shared" si="8"/>
-        <v>-13</v>
+        <v>-7</v>
       </c>
       <c r="E38">
         <v>41</v>
@@ -2473,11 +2473,11 @@
         <v>27</v>
       </c>
       <c r="C39" s="1">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D39" s="9">
         <f t="shared" si="8"/>
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="E39">
         <v>41</v>
@@ -2528,11 +2528,11 @@
         <v>9</v>
       </c>
       <c r="C40" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="8"/>
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="E40">
         <v>13</v>
@@ -2578,11 +2578,11 @@
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C42">
         <f>SUM(C30:C41)</f>
-        <v>179</v>
+        <v>262</v>
       </c>
       <c r="D42">
         <f>SUM(D30:D41)</f>
-        <v>-103</v>
+        <v>-20</v>
       </c>
       <c r="G42">
         <f>SUM(G30:G41)</f>

--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16BD902C-A54B-4E15-8DBE-20F8F347314B}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52DD00BB-9A44-46FD-B7D2-E96120F171FC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="13416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Order Bank Targets" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -409,6 +409,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1978,11 +1982,11 @@
         <v>28</v>
       </c>
       <c r="C30" s="1">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D30" s="9">
         <f>C30-B30</f>
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="E30">
         <v>41</v>
@@ -2033,11 +2037,11 @@
         <v>21</v>
       </c>
       <c r="C31" s="1">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D31" s="9">
         <f t="shared" ref="D31:D40" si="8">C31-B31</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E31">
         <v>29</v>
@@ -2088,11 +2092,11 @@
         <v>22</v>
       </c>
       <c r="C32" s="1">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D32" s="9">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E32">
         <v>33</v>
@@ -2143,11 +2147,11 @@
         <v>37</v>
       </c>
       <c r="C33" s="1">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D33" s="9">
         <f t="shared" si="8"/>
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="E33">
         <v>55</v>
@@ -2198,11 +2202,11 @@
         <v>23</v>
       </c>
       <c r="C34" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D34" s="9">
         <f t="shared" si="8"/>
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="E34">
         <v>34</v>
@@ -2253,11 +2257,11 @@
         <v>24</v>
       </c>
       <c r="C35" s="1">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D35" s="9">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E35">
         <v>37</v>
@@ -2308,11 +2312,11 @@
         <v>25</v>
       </c>
       <c r="C36" s="1">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D36" s="9">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>37</v>
@@ -2363,11 +2367,11 @@
         <v>39</v>
       </c>
       <c r="C37" s="1">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D37" s="9">
         <f t="shared" si="8"/>
-        <v>-4</v>
+        <v>7</v>
       </c>
       <c r="E37">
         <v>59</v>
@@ -2418,11 +2422,11 @@
         <v>27</v>
       </c>
       <c r="C38" s="1">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D38" s="9">
         <f t="shared" si="8"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="E38">
         <v>41</v>
@@ -2473,11 +2477,11 @@
         <v>27</v>
       </c>
       <c r="C39" s="1">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D39" s="9">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E39">
         <v>41</v>
@@ -2528,11 +2532,11 @@
         <v>9</v>
       </c>
       <c r="C40" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="8"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>13</v>
@@ -2578,11 +2582,11 @@
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C42">
         <f>SUM(C30:C41)</f>
-        <v>262</v>
+        <v>332</v>
       </c>
       <c r="D42">
         <f>SUM(D30:D41)</f>
-        <v>-20</v>
+        <v>50</v>
       </c>
       <c r="G42">
         <f>SUM(G30:G41)</f>

--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52DD00BB-9A44-46FD-B7D2-E96120F171FC}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{797CF098-5F96-43A5-BB1F-2A222715E048}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="13416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Order Bank Targets" sheetId="1" r:id="rId1"/>
@@ -138,7 +138,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,6 +148,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -267,10 +274,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -283,9 +291,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
@@ -409,10 +419,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -703,7 +709,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U42"/>
+  <dimension ref="A1:U43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
@@ -1991,10 +1997,12 @@
       <c r="E30">
         <v>41</v>
       </c>
-      <c r="F30" s="1"/>
+      <c r="F30" s="1">
+        <v>11</v>
+      </c>
       <c r="G30" s="9">
         <f>F30-E30</f>
-        <v>-41</v>
+        <v>-30</v>
       </c>
       <c r="H30">
         <v>39</v>
@@ -2037,19 +2045,21 @@
         <v>21</v>
       </c>
       <c r="C31" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31" s="9">
         <f t="shared" ref="D31:D40" si="8">C31-B31</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E31">
         <v>29</v>
       </c>
-      <c r="F31" s="1"/>
+      <c r="F31" s="1">
+        <v>10</v>
+      </c>
       <c r="G31" s="9">
         <f t="shared" ref="G31:G40" si="9">F31-E31</f>
-        <v>-29</v>
+        <v>-19</v>
       </c>
       <c r="H31">
         <v>27</v>
@@ -2092,19 +2102,21 @@
         <v>22</v>
       </c>
       <c r="C32" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D32" s="9">
         <f t="shared" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E32">
         <v>33</v>
       </c>
-      <c r="F32" s="1"/>
+      <c r="F32" s="1">
+        <v>4</v>
+      </c>
       <c r="G32" s="9">
         <f t="shared" si="9"/>
-        <v>-33</v>
+        <v>-29</v>
       </c>
       <c r="H32">
         <v>32</v>
@@ -2147,19 +2159,21 @@
         <v>37</v>
       </c>
       <c r="C33" s="1">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D33" s="9">
         <f t="shared" si="8"/>
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="E33">
         <v>55</v>
       </c>
-      <c r="F33" s="1"/>
+      <c r="F33" s="1">
+        <v>11</v>
+      </c>
       <c r="G33" s="9">
         <f t="shared" si="9"/>
-        <v>-55</v>
+        <v>-44</v>
       </c>
       <c r="H33">
         <v>51</v>
@@ -2202,19 +2216,21 @@
         <v>23</v>
       </c>
       <c r="C34" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D34" s="9">
         <f t="shared" si="8"/>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E34">
         <v>34</v>
       </c>
-      <c r="F34" s="1"/>
+      <c r="F34" s="1">
+        <v>3</v>
+      </c>
       <c r="G34" s="9">
         <f t="shared" si="9"/>
-        <v>-34</v>
+        <v>-31</v>
       </c>
       <c r="H34">
         <v>32</v>
@@ -2266,10 +2282,12 @@
       <c r="E35">
         <v>37</v>
       </c>
-      <c r="F35" s="1"/>
+      <c r="F35" s="1">
+        <v>2</v>
+      </c>
       <c r="G35" s="9">
         <f t="shared" si="9"/>
-        <v>-37</v>
+        <v>-35</v>
       </c>
       <c r="H35">
         <v>35</v>
@@ -2312,19 +2330,21 @@
         <v>25</v>
       </c>
       <c r="C36" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D36" s="9">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36">
         <v>37</v>
       </c>
-      <c r="F36" s="1"/>
+      <c r="F36" s="1">
+        <v>24</v>
+      </c>
       <c r="G36" s="9">
         <f t="shared" si="9"/>
-        <v>-37</v>
+        <v>-13</v>
       </c>
       <c r="H36">
         <v>35</v>
@@ -2367,19 +2387,21 @@
         <v>39</v>
       </c>
       <c r="C37" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D37" s="9">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E37">
         <v>59</v>
       </c>
-      <c r="F37" s="1"/>
+      <c r="F37" s="1">
+        <v>14</v>
+      </c>
       <c r="G37" s="9">
         <f t="shared" si="9"/>
-        <v>-59</v>
+        <v>-45</v>
       </c>
       <c r="H37">
         <v>55</v>
@@ -2422,19 +2444,21 @@
         <v>27</v>
       </c>
       <c r="C38" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D38" s="9">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E38">
         <v>41</v>
       </c>
-      <c r="F38" s="1"/>
+      <c r="F38" s="1">
+        <v>7</v>
+      </c>
       <c r="G38" s="9">
         <f t="shared" si="9"/>
-        <v>-41</v>
+        <v>-34</v>
       </c>
       <c r="H38">
         <v>39</v>
@@ -2486,10 +2510,12 @@
       <c r="E39">
         <v>41</v>
       </c>
-      <c r="F39" s="1"/>
+      <c r="F39" s="1">
+        <v>12</v>
+      </c>
       <c r="G39" s="9">
         <f t="shared" si="9"/>
-        <v>-41</v>
+        <v>-29</v>
       </c>
       <c r="H39">
         <v>40</v>
@@ -2541,10 +2567,12 @@
       <c r="E40">
         <v>13</v>
       </c>
-      <c r="F40" s="1"/>
+      <c r="F40" s="1">
+        <v>4</v>
+      </c>
       <c r="G40" s="10">
         <f t="shared" si="9"/>
-        <v>-13</v>
+        <v>-9</v>
       </c>
       <c r="H40">
         <v>13</v>
@@ -2580,17 +2608,21 @@
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B42">
+        <f>SUM(B30:B41)</f>
+        <v>282</v>
+      </c>
       <c r="C42">
         <f>SUM(C30:C41)</f>
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="D42">
         <f>SUM(D30:D41)</f>
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="G42">
         <f>SUM(G30:G41)</f>
-        <v>-420</v>
+        <v>-318</v>
       </c>
       <c r="J42">
         <f>SUM(J30:J41)</f>
@@ -2607,6 +2639,12 @@
       <c r="S42">
         <f>SUM(S30:S41)</f>
         <v>-305</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C43" s="12">
+        <f>C42/B42</f>
+        <v>1.2234042553191489</v>
       </c>
     </row>
   </sheetData>

--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{797CF098-5F96-43A5-BB1F-2A222715E048}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17409A1D-F52A-4979-80F8-EAAB23519D27}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="13416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -734,7 +734,7 @@
     <col min="20" max="20" width="3.88671875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6.44140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="4.109375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="6.44140625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="4.33203125" bestFit="1" customWidth="1"/>
@@ -1998,11 +1998,11 @@
         <v>41</v>
       </c>
       <c r="F30" s="1">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G30" s="9">
         <f>F30-E30</f>
-        <v>-30</v>
+        <v>-24</v>
       </c>
       <c r="H30">
         <v>39</v>
@@ -2055,11 +2055,11 @@
         <v>29</v>
       </c>
       <c r="F31" s="1">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G31" s="9">
         <f t="shared" ref="G31:G40" si="9">F31-E31</f>
-        <v>-19</v>
+        <v>-6</v>
       </c>
       <c r="H31">
         <v>27</v>
@@ -2112,11 +2112,11 @@
         <v>33</v>
       </c>
       <c r="F32" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G32" s="9">
         <f t="shared" si="9"/>
-        <v>-29</v>
+        <v>-22</v>
       </c>
       <c r="H32">
         <v>32</v>
@@ -2169,11 +2169,11 @@
         <v>55</v>
       </c>
       <c r="F33" s="1">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="G33" s="9">
         <f t="shared" si="9"/>
-        <v>-44</v>
+        <v>-23</v>
       </c>
       <c r="H33">
         <v>51</v>
@@ -2226,11 +2226,11 @@
         <v>34</v>
       </c>
       <c r="F34" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G34" s="9">
         <f t="shared" si="9"/>
-        <v>-31</v>
+        <v>-24</v>
       </c>
       <c r="H34">
         <v>32</v>
@@ -2283,11 +2283,11 @@
         <v>37</v>
       </c>
       <c r="F35" s="1">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G35" s="9">
         <f t="shared" si="9"/>
-        <v>-35</v>
+        <v>-22</v>
       </c>
       <c r="H35">
         <v>35</v>
@@ -2340,11 +2340,11 @@
         <v>37</v>
       </c>
       <c r="F36" s="1">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="G36" s="9">
         <f t="shared" si="9"/>
-        <v>-13</v>
+        <v>13</v>
       </c>
       <c r="H36">
         <v>35</v>
@@ -2397,11 +2397,11 @@
         <v>59</v>
       </c>
       <c r="F37" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G37" s="9">
         <f t="shared" si="9"/>
-        <v>-45</v>
+        <v>-39</v>
       </c>
       <c r="H37">
         <v>55</v>
@@ -2454,11 +2454,11 @@
         <v>41</v>
       </c>
       <c r="F38" s="1">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G38" s="9">
         <f t="shared" si="9"/>
-        <v>-34</v>
+        <v>-27</v>
       </c>
       <c r="H38">
         <v>39</v>
@@ -2511,11 +2511,11 @@
         <v>41</v>
       </c>
       <c r="F39" s="1">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G39" s="9">
         <f t="shared" si="9"/>
-        <v>-29</v>
+        <v>-11</v>
       </c>
       <c r="H39">
         <v>40</v>
@@ -2568,11 +2568,11 @@
         <v>13</v>
       </c>
       <c r="F40" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="9"/>
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="H40">
         <v>13</v>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="G42">
         <f>SUM(G30:G41)</f>
-        <v>-318</v>
+        <v>-192</v>
       </c>
       <c r="J42">
         <f>SUM(J30:J41)</f>

--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17409A1D-F52A-4979-80F8-EAAB23519D27}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED9B64EE-973F-4159-BA8F-0A8A16FF081B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="13416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Order Bank Targets" sheetId="1" r:id="rId1"/>
@@ -1998,11 +1998,11 @@
         <v>41</v>
       </c>
       <c r="F30" s="1">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G30" s="9">
         <f>F30-E30</f>
-        <v>-24</v>
+        <v>-14</v>
       </c>
       <c r="H30">
         <v>39</v>
@@ -2055,11 +2055,11 @@
         <v>29</v>
       </c>
       <c r="F31" s="1">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G31" s="9">
         <f t="shared" ref="G31:G40" si="9">F31-E31</f>
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="H31">
         <v>27</v>
@@ -2112,11 +2112,11 @@
         <v>33</v>
       </c>
       <c r="F32" s="1">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="G32" s="9">
         <f t="shared" si="9"/>
-        <v>-22</v>
+        <v>-7</v>
       </c>
       <c r="H32">
         <v>32</v>
@@ -2169,11 +2169,11 @@
         <v>55</v>
       </c>
       <c r="F33" s="1">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G33" s="9">
         <f t="shared" si="9"/>
-        <v>-23</v>
+        <v>-12</v>
       </c>
       <c r="H33">
         <v>51</v>
@@ -2226,11 +2226,11 @@
         <v>34</v>
       </c>
       <c r="F34" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G34" s="9">
         <f t="shared" si="9"/>
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="H34">
         <v>32</v>
@@ -2283,11 +2283,11 @@
         <v>37</v>
       </c>
       <c r="F35" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G35" s="9">
         <f t="shared" si="9"/>
-        <v>-22</v>
+        <v>-19</v>
       </c>
       <c r="H35">
         <v>35</v>
@@ -2340,11 +2340,11 @@
         <v>37</v>
       </c>
       <c r="F36" s="1">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G36" s="9">
         <f t="shared" si="9"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H36">
         <v>35</v>
@@ -2397,11 +2397,11 @@
         <v>59</v>
       </c>
       <c r="F37" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G37" s="9">
         <f t="shared" si="9"/>
-        <v>-39</v>
+        <v>-29</v>
       </c>
       <c r="H37">
         <v>55</v>
@@ -2454,11 +2454,11 @@
         <v>41</v>
       </c>
       <c r="F38" s="1">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G38" s="9">
         <f t="shared" si="9"/>
-        <v>-27</v>
+        <v>-10</v>
       </c>
       <c r="H38">
         <v>39</v>
@@ -2511,11 +2511,11 @@
         <v>41</v>
       </c>
       <c r="F39" s="1">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G39" s="9">
         <f t="shared" si="9"/>
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="H39">
         <v>40</v>
@@ -2568,11 +2568,11 @@
         <v>13</v>
       </c>
       <c r="F40" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="9"/>
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="H40">
         <v>13</v>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="G42">
         <f>SUM(G30:G41)</f>
-        <v>-192</v>
+        <v>-106</v>
       </c>
       <c r="J42">
         <f>SUM(J30:J41)</f>

--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/Weekly update/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED9B64EE-973F-4159-BA8F-0A8A16FF081B}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAE7328B-E5C4-427F-86D6-0BC71164CE37}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="13416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Order Bank Targets" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1995,14 +1995,14 @@
         <v>1</v>
       </c>
       <c r="E30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F30" s="1">
         <v>27</v>
       </c>
       <c r="G30" s="9">
         <f>F30-E30</f>
-        <v>-14</v>
+        <v>-18</v>
       </c>
       <c r="H30">
         <v>39</v>
@@ -2109,14 +2109,14 @@
         <v>17</v>
       </c>
       <c r="E32">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F32" s="1">
         <v>26</v>
       </c>
       <c r="G32" s="9">
         <f t="shared" si="9"/>
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="H32">
         <v>32</v>
@@ -2166,14 +2166,14 @@
         <v>2</v>
       </c>
       <c r="E33">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F33" s="1">
         <v>43</v>
       </c>
       <c r="G33" s="9">
         <f t="shared" si="9"/>
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="H33">
         <v>51</v>
@@ -2223,14 +2223,14 @@
         <v>-2</v>
       </c>
       <c r="E34">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F34" s="1">
         <v>14</v>
       </c>
       <c r="G34" s="9">
         <f t="shared" si="9"/>
-        <v>-20</v>
+        <v>-16</v>
       </c>
       <c r="H34">
         <v>32</v>
@@ -2280,14 +2280,14 @@
         <v>16</v>
       </c>
       <c r="E35">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F35" s="1">
         <v>18</v>
       </c>
       <c r="G35" s="9">
         <f t="shared" si="9"/>
-        <v>-19</v>
+        <v>-3</v>
       </c>
       <c r="H35">
         <v>35</v>
@@ -2337,14 +2337,14 @@
         <v>6</v>
       </c>
       <c r="E36">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="F36" s="1">
         <v>53</v>
       </c>
       <c r="G36" s="9">
         <f t="shared" si="9"/>
-        <v>16</v>
+        <v>-8</v>
       </c>
       <c r="H36">
         <v>35</v>
@@ -2394,14 +2394,14 @@
         <v>8</v>
       </c>
       <c r="E37">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="F37" s="1">
         <v>30</v>
       </c>
       <c r="G37" s="9">
         <f t="shared" si="9"/>
-        <v>-29</v>
+        <v>-9</v>
       </c>
       <c r="H37">
         <v>55</v>
@@ -2451,14 +2451,14 @@
         <v>1</v>
       </c>
       <c r="E38">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F38" s="1">
         <v>31</v>
       </c>
       <c r="G38" s="9">
         <f t="shared" si="9"/>
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H38">
         <v>39</v>
@@ -2508,14 +2508,14 @@
         <v>7</v>
       </c>
       <c r="E39">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F39" s="1">
         <v>34</v>
       </c>
       <c r="G39" s="9">
         <f t="shared" si="9"/>
-        <v>-7</v>
+        <v>-22</v>
       </c>
       <c r="H39">
         <v>40</v>
@@ -2565,14 +2565,14 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F40" s="1">
         <v>11</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="9"/>
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H40">
         <v>13</v>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="G42">
         <f>SUM(G30:G41)</f>
-        <v>-106</v>
+        <v>-114</v>
       </c>
       <c r="J42">
         <f>SUM(J30:J41)</f>

--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/Weekly update/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAE7328B-E5C4-427F-86D6-0BC71164CE37}"/>
+  <xr:revisionPtr revIDLastSave="136" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37E7C652-0E97-4862-A7C4-08F5AD99E101}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="13416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1995,14 +1995,14 @@
         <v>1</v>
       </c>
       <c r="E30">
+        <v>41</v>
+      </c>
+      <c r="F30" s="1">
         <v>45</v>
-      </c>
-      <c r="F30" s="1">
-        <v>27</v>
       </c>
       <c r="G30" s="9">
         <f>F30-E30</f>
-        <v>-18</v>
+        <v>4</v>
       </c>
       <c r="H30">
         <v>39</v>
@@ -2055,11 +2055,11 @@
         <v>29</v>
       </c>
       <c r="F31" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G31" s="9">
         <f t="shared" ref="G31:G40" si="9">F31-E31</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H31">
         <v>27</v>
@@ -2109,14 +2109,14 @@
         <v>17</v>
       </c>
       <c r="E32">
+        <v>33</v>
+      </c>
+      <c r="F32" s="1">
         <v>32</v>
-      </c>
-      <c r="F32" s="1">
-        <v>26</v>
       </c>
       <c r="G32" s="9">
         <f t="shared" si="9"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="H32">
         <v>32</v>
@@ -2166,14 +2166,14 @@
         <v>2</v>
       </c>
       <c r="E33">
+        <v>55</v>
+      </c>
+      <c r="F33" s="1">
         <v>58</v>
-      </c>
-      <c r="F33" s="1">
-        <v>43</v>
       </c>
       <c r="G33" s="9">
         <f t="shared" si="9"/>
-        <v>-15</v>
+        <v>3</v>
       </c>
       <c r="H33">
         <v>51</v>
@@ -2223,14 +2223,14 @@
         <v>-2</v>
       </c>
       <c r="E34">
+        <v>34</v>
+      </c>
+      <c r="F34" s="1">
         <v>30</v>
-      </c>
-      <c r="F34" s="1">
-        <v>14</v>
       </c>
       <c r="G34" s="9">
         <f t="shared" si="9"/>
-        <v>-16</v>
+        <v>-4</v>
       </c>
       <c r="H34">
         <v>32</v>
@@ -2280,14 +2280,14 @@
         <v>16</v>
       </c>
       <c r="E35">
+        <v>37</v>
+      </c>
+      <c r="F35" s="1">
         <v>21</v>
-      </c>
-      <c r="F35" s="1">
-        <v>18</v>
       </c>
       <c r="G35" s="9">
         <f t="shared" si="9"/>
-        <v>-3</v>
+        <v>-16</v>
       </c>
       <c r="H35">
         <v>35</v>
@@ -2337,14 +2337,14 @@
         <v>6</v>
       </c>
       <c r="E36">
+        <v>37</v>
+      </c>
+      <c r="F36" s="1">
         <v>61</v>
-      </c>
-      <c r="F36" s="1">
-        <v>53</v>
       </c>
       <c r="G36" s="9">
         <f t="shared" si="9"/>
-        <v>-8</v>
+        <v>24</v>
       </c>
       <c r="H36">
         <v>35</v>
@@ -2394,14 +2394,14 @@
         <v>8</v>
       </c>
       <c r="E37">
+        <v>59</v>
+      </c>
+      <c r="F37" s="1">
         <v>39</v>
-      </c>
-      <c r="F37" s="1">
-        <v>30</v>
       </c>
       <c r="G37" s="9">
         <f t="shared" si="9"/>
-        <v>-9</v>
+        <v>-20</v>
       </c>
       <c r="H37">
         <v>55</v>
@@ -2451,14 +2451,14 @@
         <v>1</v>
       </c>
       <c r="E38">
+        <v>41</v>
+      </c>
+      <c r="F38" s="1">
         <v>42</v>
-      </c>
-      <c r="F38" s="1">
-        <v>31</v>
       </c>
       <c r="G38" s="9">
         <f t="shared" si="9"/>
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="H38">
         <v>39</v>
@@ -2508,14 +2508,14 @@
         <v>7</v>
       </c>
       <c r="E39">
+        <v>41</v>
+      </c>
+      <c r="F39" s="1">
         <v>56</v>
-      </c>
-      <c r="F39" s="1">
-        <v>34</v>
       </c>
       <c r="G39" s="9">
         <f t="shared" si="9"/>
-        <v>-22</v>
+        <v>15</v>
       </c>
       <c r="H39">
         <v>40</v>
@@ -2565,14 +2565,14 @@
         <v>0</v>
       </c>
       <c r="E40">
+        <v>13</v>
+      </c>
+      <c r="F40" s="1">
         <v>15</v>
-      </c>
-      <c r="F40" s="1">
-        <v>11</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="9"/>
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="H40">
         <v>13</v>
@@ -2620,9 +2620,17 @@
         <f>SUM(D30:D41)</f>
         <v>63</v>
       </c>
+      <c r="E42">
+        <f>SUM(E30:E40)</f>
+        <v>420</v>
+      </c>
+      <c r="F42">
+        <f>SUM(F30:F40)</f>
+        <v>428</v>
+      </c>
       <c r="G42">
         <f>SUM(G30:G41)</f>
-        <v>-114</v>
+        <v>8</v>
       </c>
       <c r="J42">
         <f>SUM(J30:J41)</f>

--- a/order-bank.xlsx
+++ b/order-bank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rrggroup-my.sharepoint.com/personal/gavin_barry_rrg-group_com/Documents/Desktop/Weekly update/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="136" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37E7C652-0E97-4862-A7C4-08F5AD99E101}"/>
+  <xr:revisionPtr revIDLastSave="154" documentId="8_{363B32DB-CC69-4E5C-AF15-EA43B7F171F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{988532F9-7CAA-496B-A965-EADB460C5D2C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="13416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1998,19 +1998,21 @@
         <v>41</v>
       </c>
       <c r="F30" s="1">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G30" s="9">
         <f>F30-E30</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H30">
         <v>39</v>
       </c>
-      <c r="I30" s="1"/>
+      <c r="I30" s="1">
+        <v>5</v>
+      </c>
       <c r="J30" s="9">
         <f>I30-H30</f>
-        <v>-39</v>
+        <v>-34</v>
       </c>
       <c r="K30">
         <v>28</v>
@@ -2064,10 +2066,12 @@
       <c r="H31">
         <v>27</v>
       </c>
-      <c r="I31" s="1"/>
+      <c r="I31" s="1">
+        <v>5</v>
+      </c>
       <c r="J31" s="9">
         <f t="shared" ref="J31:J40" si="10">I31-H31</f>
-        <v>-27</v>
+        <v>-22</v>
       </c>
       <c r="K31">
         <v>20</v>
@@ -2112,19 +2116,21 @@
         <v>33</v>
       </c>
       <c r="F32" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G32" s="9">
         <f t="shared" si="9"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>32</v>
       </c>
-      <c r="I32" s="1"/>
+      <c r="I32" s="1">
+        <v>8</v>
+      </c>
       <c r="J32" s="9">
         <f t="shared" si="10"/>
-        <v>-32</v>
+        <v>-24</v>
       </c>
       <c r="K32">
         <v>22</v>
@@ -2178,10 +2184,12 @@
       <c r="H33">
         <v>51</v>
       </c>
-      <c r="I33" s="1"/>
+      <c r="I33" s="1">
+        <v>17</v>
+      </c>
       <c r="J33" s="9">
         <f t="shared" si="10"/>
-        <v>-51</v>
+        <v>-34</v>
       </c>
       <c r="K33">
         <v>37</v>
@@ -2235,10 +2243,12 @@
       <c r="H34">
         <v>32</v>
       </c>
-      <c r="I34" s="1"/>
+      <c r="I34" s="1">
+        <v>7</v>
+      </c>
       <c r="J34" s="9">
         <f t="shared" si="10"/>
-        <v>-32</v>
+        <v>-25</v>
       </c>
       <c r="K34">
         <v>22</v>
@@ -2292,10 +2302,12 @@
       <c r="H35">
         <v>35</v>
       </c>
-      <c r="I35" s="1"/>
+      <c r="I35" s="1">
+        <v>8</v>
+      </c>
       <c r="J35" s="9">
         <f t="shared" si="10"/>
-        <v>-35</v>
+        <v>-27</v>
       </c>
       <c r="K35">
         <v>24</v>
@@ -2349,10 +2361,12 @@
       <c r="H36">
         <v>35</v>
       </c>
-      <c r="I36" s="1"/>
+      <c r="I36" s="1">
+        <v>4</v>
+      </c>
       <c r="J36" s="9">
         <f t="shared" si="10"/>
-        <v>-35</v>
+        <v>-31</v>
       </c>
       <c r="K36">
         <v>25</v>
@@ -2406,10 +2420,12 @@
       <c r="H37">
         <v>55</v>
       </c>
-      <c r="I37" s="1"/>
+      <c r="I37" s="1">
+        <v>13</v>
+      </c>
       <c r="J37" s="9">
         <f t="shared" si="10"/>
-        <v>-55</v>
+        <v>-42</v>
       </c>
       <c r="K37">
         <v>40</v>
@@ -2463,10 +2479,12 @@
       <c r="H38">
         <v>39</v>
       </c>
-      <c r="I38" s="1"/>
+      <c r="I38" s="1">
+        <v>7</v>
+      </c>
       <c r="J38" s="9">
         <f t="shared" si="10"/>
-        <v>-39</v>
+        <v>-32</v>
       </c>
       <c r="K38">
         <v>28</v>
@@ -2511,19 +2529,21 @@
         <v>41</v>
       </c>
       <c r="F39" s="1">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G39" s="9">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H39">
         <v>40</v>
       </c>
-      <c r="I39" s="1"/>
+      <c r="I39" s="1">
+        <v>5</v>
+      </c>
       <c r="J39" s="9">
         <f t="shared" si="10"/>
-        <v>-40</v>
+        <v>-35</v>
       </c>
       <c r="K39">
         <v>28</v>
@@ -2577,10 +2597,12 @@
       <c r="H40">
         <v>13</v>
       </c>
-      <c r="I40" s="1"/>
+      <c r="I40" s="1">
+        <v>3</v>
+      </c>
       <c r="J40" s="10">
         <f t="shared" si="10"/>
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="K40">
         <v>10</v>
@@ -2626,15 +2648,15 @@
       </c>
       <c r="F42">
         <f>SUM(F30:F40)</f>
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="G42">
         <f>SUM(G30:G41)</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J42">
         <f>SUM(J30:J41)</f>
-        <v>-398</v>
+        <v>-316</v>
       </c>
       <c r="M42">
         <f>SUM(M30:M41)</f>
